--- a/ARM Functions/Item Edits/Mega Stone Damp.xlsx
+++ b/ARM Functions/Item Edits/Mega Stone Damp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Item Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413B1BB9-718B-4CB8-8D8D-9417C3EED1C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA07F1E-2AAD-4770-AD10-300A5B6112A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{6B563214-6527-4E5F-B5EA-E821D6DED3A7}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="86">
   <si>
     <t>notes</t>
   </si>
@@ -102,12 +102,6 @@
     <t>bl 0x00092298</t>
   </si>
   <si>
-    <t>ldrh r0, [r0, 0xC]</t>
-  </si>
-  <si>
-    <t>BC00D0E1</t>
-  </si>
-  <si>
     <t>mov r0, 0x12</t>
   </si>
   <si>
@@ -168,66 +162,12 @@
     <t>mov r1, r2</t>
   </si>
   <si>
-    <t>get species</t>
-  </si>
-  <si>
-    <t>get table</t>
-  </si>
-  <si>
-    <t>0020A0E3</t>
-  </si>
-  <si>
-    <t>mov r2, 0x0</t>
-  </si>
-  <si>
-    <t>B23091E1</t>
-  </si>
-  <si>
-    <t>ldrh r3, [r1, r2]</t>
-  </si>
-  <si>
-    <t>030050E1</t>
-  </si>
-  <si>
-    <t>cmp r0, r3</t>
-  </si>
-  <si>
-    <t>0300000A</t>
-  </si>
-  <si>
-    <t>000050E3</t>
-  </si>
-  <si>
-    <t>cmp r0, 0x0</t>
-  </si>
-  <si>
-    <t>022082E2</t>
-  </si>
-  <si>
-    <t>add r2, r2, 0x2</t>
-  </si>
-  <si>
-    <t>F8FFFFEA</t>
-  </si>
-  <si>
     <t>0F40BDE8</t>
   </si>
   <si>
     <t>0F80BDE8</t>
   </si>
   <si>
-    <t>Table of valid Pokemon</t>
-  </si>
-  <si>
-    <t>Table</t>
-  </si>
-  <si>
-    <t>Gengar</t>
-  </si>
-  <si>
-    <t>0014AF20</t>
-  </si>
-  <si>
     <t>mov r5, r3</t>
   </si>
   <si>
@@ -345,28 +285,37 @@
     <t>A940FEEB</t>
   </si>
   <si>
-    <t>3C109FE5</t>
-  </si>
-  <si>
-    <t>0800000A</t>
-  </si>
-  <si>
     <t>040059E3</t>
   </si>
   <si>
-    <t>A276FD0A</t>
-  </si>
-  <si>
-    <t>0767FF3A</t>
-  </si>
-  <si>
     <t>250059E3</t>
   </si>
   <si>
-    <t>0D62FF0A</t>
-  </si>
-  <si>
-    <t>255DFF8A</t>
+    <t>bl 0x000D6F98</t>
+  </si>
+  <si>
+    <t>cmp r1, 0x1</t>
+  </si>
+  <si>
+    <t>E853FFEB</t>
+  </si>
+  <si>
+    <t>010051E3</t>
+  </si>
+  <si>
+    <t>0600001A</t>
+  </si>
+  <si>
+    <t>A976FD0A</t>
+  </si>
+  <si>
+    <t>0E67FF3A</t>
+  </si>
+  <si>
+    <t>1462FF0A</t>
+  </si>
+  <si>
+    <t>2C5DFF8A</t>
   </si>
 </sst>
 </file>
@@ -433,7 +382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -442,9 +391,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -780,7 +726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B45B0BF-76E7-4635-9005-9D6B1877FAE8}">
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr defaultRowHeight="15.9"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -817,14 +763,14 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B3" s="2" t="str">
         <f>_xlfn.CONCAT("0",RIGHT(C3,1),"10A0E3")</f>
         <v>0410A0E3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="D3" s="1"/>
     </row>
@@ -882,18 +828,18 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -902,25 +848,25 @@
         <v>00101FE4</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="str">
-        <f t="shared" ref="A12:A32" si="1">DEC2HEX(HEX2DEC(A11)+4,8)</f>
+        <f t="shared" ref="A12:A24" si="1">DEC2HEX(HEX2DEC(A11)+4,8)</f>
         <v>00101FE8</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D12" s="5"/>
     </row>
@@ -930,7 +876,7 @@
         <v>00101FEC</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>13</v>
@@ -943,29 +889,23 @@
         <v>00101FF0</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>36</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="str">
         <f t="shared" si="1"/>
         <v>00101FF4</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C15" s="2" t="str">
-        <f>_xlfn.CONCAT("ldr r1, [pc, #",HEX2DEC(A32)-HEX2DEC(A15)-8,"]")</f>
-        <v>ldr r1, [pc, #60]</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>37</v>
+      <c r="B15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -974,10 +914,11 @@
         <v>00101FF8</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
+      </c>
+      <c r="C16" s="2" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A24)</f>
+        <v>bne 0x00102018</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -986,10 +927,11 @@
         <v>00101FFC</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
+      </c>
+      <c r="C17" s="2" t="str">
+        <f>SUBSTITUTE(C10,"push","pop")</f>
+        <v>pop {r0, r1, r2, r3, lr}</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -998,10 +940,10 @@
         <v>00102000</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1010,11 +952,13 @@
         <v>00102004</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="2" t="str">
-        <f>_xlfn.CONCAT("beq 0x",A24)</f>
-        <v>beq 0x00102018</v>
+        <v>82</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1022,11 +966,14 @@
         <f t="shared" si="1"/>
         <v>00102008</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>45</v>
+      <c r="B20" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>46</v>
+        <v>73</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1034,12 +981,11 @@
         <f t="shared" si="1"/>
         <v>0010200C</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C21" s="2" t="str">
-        <f>_xlfn.CONCAT("beq 0x",A31)</f>
-        <v>beq 0x00102034</v>
+      <c r="B21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1047,11 +993,15 @@
         <f t="shared" si="1"/>
         <v>00102010</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>48</v>
+      <c r="B22" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="2" t="str">
+        <f>_xlfn.CONCAT("beq 0x",A27)</f>
+        <v>beq 0x000DA868</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1060,11 +1010,13 @@
         <v>00102014</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="2" t="str">
-        <f>_xlfn.CONCAT("b 0x",A17)</f>
-        <v>b 0x00101FFC</v>
+        <v>85</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1073,640 +1025,293 @@
         <v>00102018</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C24" s="2" t="str">
-        <f>SUBSTITUTE(C10,"push","pop")</f>
-        <v>pop {r0, r1, r2, r3, lr}</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>0010201C</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>66</v>
+        <f>SUBSTITUTE(C17,"lr","pc")</f>
+        <v>pop {r0, r1, r2, r3, pc}</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00102020</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>69</v>
+      <c r="A26" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00102024</v>
+      <c r="A27" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00102028</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>100</v>
+        <f t="shared" ref="A28:A47" si="2">DEC2HEX(HEX2DEC(A27)+4,8)</f>
+        <v>000DA86C</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>0010202C</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C29" s="2" t="str">
-        <f>_xlfn.CONCAT("beq 0x",A35)</f>
-        <v>beq 0x000DA868</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>71</v>
+      <c r="A29" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA870</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00102030</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>72</v>
-      </c>
+      <c r="A30" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA874</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="7"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00102034</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" s="2" t="str">
-        <f>SUBSTITUTE(C24,"lr","pc")</f>
-        <v>pop {r0, r1, r2, r3, pc}</v>
-      </c>
+      <c r="A31" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA878</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="7"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00102038</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>52</v>
-      </c>
+      <c r="A32" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA87C</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA880</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="5" t="str">
+        <f>_xlfn.CONCAT("beq 0x",A37)</f>
+        <v>beq 0x000DA890</v>
+      </c>
+      <c r="D33" s="5"/>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="A34" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA884</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" s="5"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="A35" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA888</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" s="5"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="2" t="str">
-        <f t="shared" ref="A36:A55" si="2">DEC2HEX(HEX2DEC(A35)+4,8)</f>
-        <v>000DA86C</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>56</v>
-      </c>
+      <c r="A36" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA88C</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" s="5" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A47)</f>
+        <v>bne 0x000DA8B8</v>
+      </c>
+      <c r="D36" s="5"/>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>000DA870</v>
+        <v>000DA890</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>17</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D37" s="7"/>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>000DA874</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>78</v>
+        <v>000DA894</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>66</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="D38" s="7"/>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>000DA878</v>
+        <v>000DA898</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="D39" s="7"/>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA87C</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>58</v>
-      </c>
+      <c r="A40" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA89C</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" s="7"/>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA880</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C41" s="5" t="str">
-        <f>_xlfn.CONCAT("beq 0x",A45)</f>
-        <v>beq 0x000DA890</v>
-      </c>
-      <c r="D41" s="5"/>
+      <c r="A41" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA8A0</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41" s="7"/>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA884</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D42" s="5"/>
+      <c r="A42" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA8A4</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" s="7" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A47)</f>
+        <v>bne 0x000DA8B8</v>
+      </c>
+      <c r="D42" s="7"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA888</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D43" s="5"/>
+      <c r="A43" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA8A8</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA88C</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C44" s="5" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A55)</f>
-        <v>bne 0x000DA8B8</v>
-      </c>
-      <c r="D44" s="5"/>
+      <c r="A44" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA8AC</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA890</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D45" s="7"/>
+      <c r="A45" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA8B0</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="2" t="str">
+        <f>SUBSTITUTE(C27,"push","pop")</f>
+        <v>pop {r4, r5, lr}</v>
+      </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA894</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D46" s="7"/>
+      <c r="A46" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA8B4</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA898</v>
-      </c>
-      <c r="B47" s="7" t="s">
+      <c r="A47" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA8B8</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D47" s="7"/>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA89C</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D48" s="7"/>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA8A0</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D49" s="7"/>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA8A4</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="7" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A55)</f>
-        <v>bne 0x000DA8B8</v>
-      </c>
-      <c r="D50" s="7"/>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA8A8</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA8AC</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA8B0</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C53" s="2" t="str">
-        <f>SUBSTITUTE(C35,"push","pop")</f>
-        <v>pop {r4, r5, lr}</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA8B4</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA8B8</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C55" s="2" t="str">
-        <f>SUBSTITUTE(C53,"lr","pc")</f>
+      <c r="C47" s="2" t="str">
+        <f>SUBSTITUTE(C45,"lr","pc")</f>
         <v>pop {r4, r5, pc}</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B58" s="2" t="str">
-        <f>RIGHT(E58,2)&amp;LEFT(E58,2)</f>
-        <v>5E00</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D58" s="2">
-        <v>94</v>
-      </c>
-      <c r="E58" s="2" t="str">
-        <f>DEC2HEX(D58,4)</f>
-        <v>005E</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="2" t="str">
-        <f>DEC2HEX(HEX2DEC(A58)+2,8)</f>
-        <v>0014AF22</v>
-      </c>
-      <c r="B59" s="2" t="str">
-        <f t="shared" ref="B59:B73" si="3">RIGHT(E59,2)&amp;LEFT(E59,2)</f>
-        <v>0000</v>
-      </c>
-      <c r="C59" s="8"/>
-      <c r="E59" s="2" t="str">
-        <f t="shared" ref="E59:E73" si="4">DEC2HEX(D59,4)</f>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="2" t="str">
-        <f t="shared" ref="A60:A73" si="5">DEC2HEX(HEX2DEC(A59)+2,8)</f>
-        <v>0014AF24</v>
-      </c>
-      <c r="B60" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-      <c r="C60" s="8"/>
-      <c r="E60" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>0014AF26</v>
-      </c>
-      <c r="B61" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-      <c r="C61" s="8"/>
-      <c r="E61" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>0014AF28</v>
-      </c>
-      <c r="B62" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-      <c r="E62" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>0014AF2A</v>
-      </c>
-      <c r="B63" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-      <c r="E63" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>0014AF2C</v>
-      </c>
-      <c r="B64" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-      <c r="E64" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>0014AF2E</v>
-      </c>
-      <c r="B65" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-      <c r="E65" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>0014AF30</v>
-      </c>
-      <c r="B66" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-      <c r="E66" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>0014AF32</v>
-      </c>
-      <c r="B67" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-      <c r="E67" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>0014AF34</v>
-      </c>
-      <c r="B68" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-      <c r="E68" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>0014AF36</v>
-      </c>
-      <c r="B69" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-      <c r="E69" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>0014AF38</v>
-      </c>
-      <c r="B70" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-      <c r="E70" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>0014AF3A</v>
-      </c>
-      <c r="B71" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-      <c r="E71" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>0014AF3C</v>
-      </c>
-      <c r="B72" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-      <c r="E72" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>0014AF3E</v>
-      </c>
-      <c r="B73" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-      <c r="E73" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0000</v>
       </c>
     </row>
   </sheetData>
